--- a/docs/DATA_STRUCTURE.xlsx
+++ b/docs/DATA_STRUCTURE.xlsx
@@ -9,10 +9,11 @@
     <sheet name="Table - imports" sheetId="4" r:id="rId4"/>
     <sheet name="Table - record_pool" sheetId="5" r:id="rId5"/>
     <sheet name="Table - import_rows" sheetId="6" r:id="rId6"/>
-    <sheet name="ParseSummary" sheetId="7" r:id="rId7"/>
-    <sheet name="ChangeSummary" sheetId="8" r:id="rId8"/>
-    <sheet name="Computed Fields" sheetId="9" r:id="rId9"/>
-    <sheet name="API Endpoints" sheetId="10" r:id="rId10"/>
+    <sheet name="Table - upload_staging" sheetId="7" r:id="rId7"/>
+    <sheet name="ParseSummary" sheetId="8" r:id="rId8"/>
+    <sheet name="ChangeSummary" sheetId="9" r:id="rId9"/>
+    <sheet name="Computed Fields" sheetId="10" r:id="rId10"/>
+    <sheet name="API Endpoints" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -435,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Header is on row 3. Fill data from row 4 onward. Keep these column names exactly.</v>
+        <v>Header row is auto-detected (the row containing 'Project Code'); data starts on the next row. Keep these column names exactly.</v>
       </c>
     </row>
     <row r="3">
@@ -671,7 +672,83 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="56.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Recomputed on every read (not stored)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C2" t="str">
+        <v>How it is computed</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ageingDays</v>
+      </c>
+      <c r="B3" t="str">
+        <v>integer/null</v>
+      </c>
+      <c r="C3" t="str">
+        <v>today - assignDate in whole UTC days; null if no date</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ageing color</v>
+      </c>
+      <c r="B4" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="C4" t="str">
+        <v>green &lt;=30, amber 31-60, red &gt;60, neutral when no date</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>routeSteps</v>
+      </c>
+      <c r="B5" t="str">
+        <v>string[]</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Operation string split on commas (trimmed)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>currentStepIndex</v>
+      </c>
+      <c r="B6" t="str">
+        <v>integer/null</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Index of activity within routeSteps, else null</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -719,122 +796,166 @@
         <v>multipart: file (req), label, reportDate</v>
       </c>
       <c r="C4" t="str">
-        <v>Created import + change set</v>
+        <v>Created import + change set (direct, no gate)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>DELETE /imports</v>
+        <v>POST /imports/stage</v>
       </c>
       <c r="B5" t="str">
-        <v>none</v>
+        <v>multipart: file (req), label, reportDate</v>
       </c>
       <c r="C5" t="str">
-        <v>{ importsDeleted, poolRowsDeleted } — full reset</v>
+        <v>{ stagingId, sourceFilename, structural } — holds the file; nothing committed</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GET /imports/{id}</v>
+        <v>POST /imports/validate</v>
       </c>
       <c r="B6" t="str">
-        <v>path id</v>
+        <v>json { stagingId }</v>
       </c>
       <c r="C6" t="str">
-        <v>One import with summaries</v>
+        <v>Gatekeeper verdict (ok/reject) + descriptive-only sanitize suggestions (advisory)</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DELETE /imports/{id}</v>
+        <v>POST /imports/commit</v>
       </c>
       <c r="B7" t="str">
-        <v>path id</v>
+        <v>json { stagingId, acceptedSuggestions? }</v>
       </c>
       <c r="C7" t="str">
-        <v>204; deletes the import only (pool stays)</v>
+        <v>Applies accepted (field,from)-&gt;to cleanups, merges, returns created import + change set</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GET /imports/{id}/records</v>
+        <v>DELETE /imports/stage/{id}</v>
       </c>
       <c r="B8" t="str">
         <v>path id</v>
       </c>
       <c r="C8" t="str">
-        <v>Records, copy-expanded, with live ageing/route</v>
+        <v>204; discards a staged upload without committing</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GET /imports/{id}/changes</v>
+        <v>DELETE /imports</v>
       </c>
       <c r="B9" t="str">
-        <v>path id</v>
+        <v>none</v>
       </c>
       <c r="C9" t="str">
-        <v>Change set vs previous import</v>
+        <v>{ importsDeleted, poolRowsDeleted } — full reset</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GET /imports/compare</v>
+        <v>GET /imports/{id}</v>
       </c>
       <c r="B10" t="str">
-        <v>query from (req), to (req)</v>
+        <v>path id</v>
       </c>
       <c r="C10" t="str">
-        <v>Change set between any two imports</v>
+        <v>One import with summaries</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GET /ai/status</v>
+        <v>DELETE /imports/{id}</v>
       </c>
       <c r="B11" t="str">
-        <v>none</v>
+        <v>path id</v>
       </c>
       <c r="C11" t="str">
-        <v>{ available }</v>
+        <v>204; deletes the import only (pool stays)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>POST /ai/sanitize</v>
+        <v>GET /imports/{id}/records</v>
       </c>
       <c r="B12" t="str">
-        <v>json { importId }</v>
+        <v>path id</v>
       </c>
       <c r="C12" t="str">
-        <v>Suggested descriptive-field cleanups (advisory)</v>
+        <v>Records, copy-expanded, with live ageing/route</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>POST /ai/review</v>
+        <v>GET /imports/{id}/changes</v>
       </c>
       <c r="B13" t="str">
-        <v>json { importId, compareTo?, deep? }</v>
+        <v>path id</v>
       </c>
       <c r="C13" t="str">
-        <v>Consistency audit (advisory, read-only)</v>
+        <v>Change set vs previous import</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>GET /imports/compare</v>
+      </c>
+      <c r="B14" t="str">
+        <v>query from (req), to (req)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Change set between any two imports</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>GET /ai/status</v>
+      </c>
+      <c r="B15" t="str">
+        <v>none</v>
+      </c>
+      <c r="C15" t="str">
+        <v>{ available }</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>POST /ai/sanitize</v>
+      </c>
+      <c r="B16" t="str">
+        <v>json { importId }</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Suggested descriptive-field cleanups (advisory)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>POST /ai/review</v>
+      </c>
+      <c r="B17" t="str">
+        <v>json { importId, compareTo?, deep? }</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Consistency audit (advisory, read-only)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>POST /ai/report</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B18" t="str">
         <v>json { importId, compareTo?, filters? }</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C18" t="str">
         <v>Turnaround analytical report (advisory)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1375,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1417,7 +1538,7 @@
         <v>text unique</v>
       </c>
       <c r="C4" t="str">
-        <v>SHA-256 of all 18 normalized fields; identical rows share it</v>
+        <v>SHA-256 of the original 18 source fields; identical rows share it (derived mark fields excluded)</v>
       </c>
     </row>
     <row r="5">
@@ -1439,7 +1560,7 @@
         <v>text</v>
       </c>
       <c r="C6" t="str">
-        <v>Derived from Alias</v>
+        <v>= alias_corrected</v>
       </c>
     </row>
     <row r="7">
@@ -1450,7 +1571,7 @@
         <v>text</v>
       </c>
       <c r="C7" t="str">
-        <v>Mark No. with '&lt;job&gt; &lt;alias&gt;-' prefix stripped</v>
+        <v>= m_no</v>
       </c>
     </row>
     <row r="8">
@@ -1461,199 +1582,243 @@
         <v>text</v>
       </c>
       <c r="C8" t="str">
-        <v>job\structure\markTail (human-facing identity)</v>
+        <v>= mark_number (human-facing + change-log identity)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>order_nature</v>
+        <v>m_no</v>
       </c>
       <c r="B9" t="str">
-        <v>text/null</v>
+        <v>text</v>
       </c>
       <c r="C9" t="str">
-        <v>Order Nature</v>
+        <v>Parsed bare mark tail (e.g. M101); notNull default ''</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>contractor</v>
+        <v>project_suffix</v>
       </c>
       <c r="B10" t="str">
-        <v>text/null</v>
+        <v>text</v>
       </c>
       <c r="C10" t="str">
-        <v>Contractor</v>
+        <v>Project segment of a backslash mark, else ''; notNull default ''</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>job_card_no</v>
+        <v>alias_corrected</v>
       </c>
       <c r="B11" t="str">
-        <v>text/null</v>
+        <v>text</v>
       </c>
       <c r="C11" t="str">
-        <v>Job Card No.</v>
+        <v>Structure/alias resolved from the mark (falls back to Alias); notNull default ''</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>tower_type</v>
+        <v>mark_number</v>
       </c>
       <c r="B12" t="str">
-        <v>text/null</v>
+        <v>text</v>
       </c>
       <c r="C12" t="str">
-        <v>Tower Type</v>
+        <v>job\alias_corrected\m_no (canonical backslash identity); notNull default ''</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>tower_sub_type</v>
+        <v>order_nature</v>
       </c>
       <c r="B13" t="str">
         <v>text/null</v>
       </c>
       <c r="C13" t="str">
-        <v>Tower Sub Type</v>
+        <v>Order Nature</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>alias</v>
+        <v>contractor</v>
       </c>
       <c r="B14" t="str">
         <v>text/null</v>
       </c>
       <c r="C14" t="str">
-        <v>Alias</v>
+        <v>Contractor</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mark_no</v>
+        <v>job_card_no</v>
       </c>
       <c r="B15" t="str">
-        <v>text</v>
+        <v>text/null</v>
       </c>
       <c r="C15" t="str">
-        <v>Mark No. (raw)</v>
+        <v>Job Card No.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>section</v>
+        <v>tower_type</v>
       </c>
       <c r="B16" t="str">
         <v>text/null</v>
       </c>
       <c r="C16" t="str">
-        <v>Section</v>
+        <v>Tower Type</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>length</v>
+        <v>tower_sub_type</v>
       </c>
       <c r="B17" t="str">
-        <v>number/null</v>
+        <v>text/null</v>
       </c>
       <c r="C17" t="str">
-        <v>Length</v>
+        <v>Tower Sub Type</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>width</v>
+        <v>alias</v>
       </c>
       <c r="B18" t="str">
-        <v>number/null</v>
+        <v>text/null</v>
       </c>
       <c r="C18" t="str">
-        <v>Width</v>
+        <v>Alias</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>wt_pcs</v>
+        <v>mark_no</v>
       </c>
       <c r="B19" t="str">
-        <v>number/null</v>
+        <v>text</v>
       </c>
       <c r="C19" t="str">
-        <v>Wt/Pcs</v>
+        <v>Mark No. (raw)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>balance_qty</v>
+        <v>section</v>
       </c>
       <c r="B20" t="str">
-        <v>number</v>
+        <v>text/null</v>
       </c>
       <c r="C20" t="str">
-        <v>Balance Qty. (defaults 0)</v>
+        <v>Section</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>balance_wt</v>
+        <v>length</v>
       </c>
       <c r="B21" t="str">
-        <v>number</v>
+        <v>number/null</v>
       </c>
       <c r="C21" t="str">
-        <v>Balance Wt. (defaults 0)</v>
+        <v>Length</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>assign_date</v>
+        <v>width</v>
       </c>
       <c r="B22" t="str">
-        <v>date/null</v>
+        <v>number/null</v>
       </c>
       <c r="C22" t="str">
-        <v>Assign Date, normalized YYYY-MM-DD</v>
+        <v>Width</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>activity</v>
+        <v>wt_pcs</v>
       </c>
       <c r="B23" t="str">
-        <v>text/null</v>
+        <v>number/null</v>
       </c>
       <c r="C23" t="str">
-        <v>Activity</v>
+        <v>Wt/Pcs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>operation</v>
+        <v>balance_qty</v>
       </c>
       <c r="B24" t="str">
-        <v>text/null</v>
+        <v>number</v>
       </c>
       <c r="C24" t="str">
-        <v>Operation</v>
+        <v>Balance Qty. (defaults 0)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>balance_wt</v>
+      </c>
+      <c r="B25" t="str">
+        <v>number</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Balance Wt. (defaults 0)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>assign_date</v>
+      </c>
+      <c r="B26" t="str">
+        <v>date/null</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Assign Date, normalized YYYY-MM-DD</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>activity</v>
+      </c>
+      <c r="B27" t="str">
+        <v>text/null</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Activity</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>operation</v>
+      </c>
+      <c r="B28" t="str">
+        <v>text/null</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Operation</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>ref_job_card_no</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B29" t="str">
         <v>text/null</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C29" t="str">
         <v>Ref. Job Card No.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1725,6 +1890,104 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="56.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Temporary holding for the gatekeeper flow; nothing is committed until the user accepts. Removed on commit or discard.</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Column</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>id</v>
+      </c>
+      <c r="B3" t="str">
+        <v>text (uuid) PK</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Staging id returned by POST /imports/stage</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>source_filename</v>
+      </c>
+      <c r="B4" t="str">
+        <v>text</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Original file name</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>label</v>
+      </c>
+      <c r="B5" t="str">
+        <v>text/null</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Friendly name (optional)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>report_date</v>
+      </c>
+      <c r="B6" t="str">
+        <v>date/null</v>
+      </c>
+      <c r="C6" t="str">
+        <v>'As of' date (optional)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>file_data</v>
+      </c>
+      <c r="B7" t="str">
+        <v>bytea</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Raw uploaded .xlsx bytes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="B8" t="str">
+        <v>timestamp</v>
+      </c>
+      <c r="C8" t="str">
+        <v>When it was staged</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C9"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
@@ -1832,7 +2095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
   <cols>
@@ -1972,80 +2235,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="56.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Recomputed on every read (not stored)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C2" t="str">
-        <v>How it is computed</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ageingDays</v>
-      </c>
-      <c r="B3" t="str">
-        <v>integer/null</v>
-      </c>
-      <c r="C3" t="str">
-        <v>today - assignDate in whole UTC days; null if no date</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ageing color</v>
-      </c>
-      <c r="B4" t="str">
-        <v>n/a</v>
-      </c>
-      <c r="C4" t="str">
-        <v>green &lt;=30, amber 31-60, red &gt;60, neutral when no date</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>routeSteps</v>
-      </c>
-      <c r="B5" t="str">
-        <v>string[]</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Operation string split on commas (trimmed)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>currentStepIndex</v>
-      </c>
-      <c r="B6" t="str">
-        <v>integer/null</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Index of activity within routeSteps, else null</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
 </file>